--- a/data/2026-05-08/BallparkPal_Games.xlsx
+++ b/data/2026-05-08/BallparkPal_Games.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>GamePk</t>
   </si>
@@ -144,6 +144,66 @@
   </si>
   <si>
     <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>ATH</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>ARI</t>
   </si>
 </sst>
 </file>
@@ -483,7 +543,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -622,112 +682,1332 @@
         <v>42</v>
       </c>
       <c r="E2">
-        <v>3.985</v>
+        <v>3.839</v>
       </c>
       <c r="F2">
-        <v>5.282</v>
+        <v>4.892</v>
       </c>
       <c r="G2">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="H2">
-        <v>0.649</v>
+        <v>0.633</v>
       </c>
       <c r="I2">
-        <v>0.176</v>
+        <v>0.186</v>
       </c>
       <c r="J2">
-        <v>0.073</v>
+        <v>0.077</v>
       </c>
       <c r="K2">
-        <v>0.102</v>
+        <v>0.105</v>
       </c>
       <c r="L2">
-        <v>0.369</v>
+        <v>0.337</v>
       </c>
       <c r="M2">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
       <c r="N2">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="O2">
-        <v>0.547</v>
+        <v>0.508</v>
       </c>
       <c r="P2">
-        <v>2.28</v>
+        <v>2.102</v>
       </c>
       <c r="Q2">
-        <v>3.133</v>
+        <v>2.93</v>
       </c>
       <c r="R2">
-        <v>0.332</v>
+        <v>0.318</v>
       </c>
       <c r="S2">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="T2">
         <v>0.0</v>
       </c>
       <c r="U2">
+        <v>0.015</v>
+      </c>
+      <c r="V2">
+        <v>0.019</v>
+      </c>
+      <c r="W2">
+        <v>0.058</v>
+      </c>
+      <c r="X2">
+        <v>0.042</v>
+      </c>
+      <c r="Y2">
+        <v>0.098</v>
+      </c>
+      <c r="Z2">
+        <v>0.091</v>
+      </c>
+      <c r="AA2">
+        <v>0.117</v>
+      </c>
+      <c r="AB2">
+        <v>0.08</v>
+      </c>
+      <c r="AC2">
+        <v>0.104</v>
+      </c>
+      <c r="AD2">
+        <v>0.07</v>
+      </c>
+      <c r="AE2">
+        <v>0.076</v>
+      </c>
+      <c r="AF2">
+        <v>0.054</v>
+      </c>
+      <c r="AG2">
+        <v>0.048</v>
+      </c>
+      <c r="AH2">
+        <v>0.028</v>
+      </c>
+      <c r="AI2">
+        <v>0.028</v>
+      </c>
+      <c r="AJ2">
+        <v>0.021</v>
+      </c>
+      <c r="AK2">
+        <v>0.019</v>
+      </c>
+      <c r="AL2">
+        <v>0.009</v>
+      </c>
+      <c r="AM2">
+        <v>0.011</v>
+      </c>
+      <c r="AN2">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3">
+        <v>823957</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>4.11</v>
+      </c>
+      <c r="F3">
+        <v>4.597</v>
+      </c>
+      <c r="G3">
+        <v>0.427</v>
+      </c>
+      <c r="H3">
+        <v>0.573</v>
+      </c>
+      <c r="I3">
+        <v>0.216</v>
+      </c>
+      <c r="J3">
+        <v>0.096</v>
+      </c>
+      <c r="K3">
+        <v>0.115</v>
+      </c>
+      <c r="L3">
+        <v>0.277</v>
+      </c>
+      <c r="M3">
+        <v>0.106</v>
+      </c>
+      <c r="N3">
+        <v>0.19</v>
+      </c>
+      <c r="O3">
+        <v>0.503</v>
+      </c>
+      <c r="P3">
+        <v>2.268</v>
+      </c>
+      <c r="Q3">
+        <v>2.545</v>
+      </c>
+      <c r="R3">
+        <v>0.393</v>
+      </c>
+      <c r="S3">
+        <v>0.448</v>
+      </c>
+      <c r="T3">
+        <v>0.0</v>
+      </c>
+      <c r="U3">
+        <v>0.019</v>
+      </c>
+      <c r="V3">
+        <v>0.02</v>
+      </c>
+      <c r="W3">
+        <v>0.058</v>
+      </c>
+      <c r="X3">
+        <v>0.047</v>
+      </c>
+      <c r="Y3">
+        <v>0.096</v>
+      </c>
+      <c r="Z3">
+        <v>0.077</v>
+      </c>
+      <c r="AA3">
+        <v>0.107</v>
+      </c>
+      <c r="AB3">
+        <v>0.082</v>
+      </c>
+      <c r="AC3">
+        <v>0.113</v>
+      </c>
+      <c r="AD3">
+        <v>0.078</v>
+      </c>
+      <c r="AE3">
+        <v>0.081</v>
+      </c>
+      <c r="AF3">
+        <v>0.052</v>
+      </c>
+      <c r="AG3">
+        <v>0.052</v>
+      </c>
+      <c r="AH3">
+        <v>0.027</v>
+      </c>
+      <c r="AI3">
+        <v>0.031</v>
+      </c>
+      <c r="AJ3">
+        <v>0.018</v>
+      </c>
+      <c r="AK3">
+        <v>0.015</v>
+      </c>
+      <c r="AL3">
+        <v>0.01</v>
+      </c>
+      <c r="AM3">
+        <v>0.005</v>
+      </c>
+      <c r="AN3">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4">
+        <v>824116</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4">
+        <v>4.119</v>
+      </c>
+      <c r="F4">
+        <v>4.329</v>
+      </c>
+      <c r="G4">
+        <v>0.455</v>
+      </c>
+      <c r="H4">
+        <v>0.545</v>
+      </c>
+      <c r="I4">
+        <v>0.234</v>
+      </c>
+      <c r="J4">
+        <v>0.098</v>
+      </c>
+      <c r="K4">
+        <v>0.123</v>
+      </c>
+      <c r="L4">
+        <v>0.247</v>
+      </c>
+      <c r="M4">
+        <v>0.105</v>
+      </c>
+      <c r="N4">
+        <v>0.193</v>
+      </c>
+      <c r="O4">
+        <v>0.484</v>
+      </c>
+      <c r="P4">
+        <v>2.186</v>
+      </c>
+      <c r="Q4">
+        <v>2.399</v>
+      </c>
+      <c r="R4">
+        <v>0.388</v>
+      </c>
+      <c r="S4">
+        <v>0.451</v>
+      </c>
+      <c r="T4">
+        <v>0.0</v>
+      </c>
+      <c r="U4">
+        <v>0.016</v>
+      </c>
+      <c r="V4">
+        <v>0.019</v>
+      </c>
+      <c r="W4">
+        <v>0.065</v>
+      </c>
+      <c r="X4">
+        <v>0.054</v>
+      </c>
+      <c r="Y4">
+        <v>0.104</v>
+      </c>
+      <c r="Z4">
+        <v>0.078</v>
+      </c>
+      <c r="AA4">
+        <v>0.125</v>
+      </c>
+      <c r="AB4">
+        <v>0.084</v>
+      </c>
+      <c r="AC4">
+        <v>0.103</v>
+      </c>
+      <c r="AD4">
+        <v>0.07</v>
+      </c>
+      <c r="AE4">
+        <v>0.081</v>
+      </c>
+      <c r="AF4">
+        <v>0.042</v>
+      </c>
+      <c r="AG4">
+        <v>0.05</v>
+      </c>
+      <c r="AH4">
+        <v>0.031</v>
+      </c>
+      <c r="AI4">
+        <v>0.02</v>
+      </c>
+      <c r="AJ4">
+        <v>0.015</v>
+      </c>
+      <c r="AK4">
+        <v>0.014</v>
+      </c>
+      <c r="AL4">
+        <v>0.008</v>
+      </c>
+      <c r="AM4">
+        <v>0.007</v>
+      </c>
+      <c r="AN4">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40">
+      <c r="A5">
+        <v>824607</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>4.004</v>
+      </c>
+      <c r="F5">
+        <v>3.564</v>
+      </c>
+      <c r="G5">
+        <v>0.526</v>
+      </c>
+      <c r="H5">
+        <v>0.474</v>
+      </c>
+      <c r="I5">
+        <v>0.277</v>
+      </c>
+      <c r="J5">
+        <v>0.11</v>
+      </c>
+      <c r="K5">
+        <v>0.139</v>
+      </c>
+      <c r="L5">
+        <v>0.195</v>
+      </c>
+      <c r="M5">
+        <v>0.097</v>
+      </c>
+      <c r="N5">
+        <v>0.182</v>
+      </c>
+      <c r="O5">
+        <v>0.44</v>
+      </c>
+      <c r="P5">
+        <v>2.103</v>
+      </c>
+      <c r="Q5">
+        <v>1.939</v>
+      </c>
+      <c r="R5">
+        <v>0.435</v>
+      </c>
+      <c r="S5">
+        <v>0.381</v>
+      </c>
+      <c r="T5">
+        <v>0.001</v>
+      </c>
+      <c r="U5">
+        <v>0.029</v>
+      </c>
+      <c r="V5">
+        <v>0.027</v>
+      </c>
+      <c r="W5">
+        <v>0.089</v>
+      </c>
+      <c r="X5">
+        <v>0.071</v>
+      </c>
+      <c r="Y5">
+        <v>0.122</v>
+      </c>
+      <c r="Z5">
+        <v>0.092</v>
+      </c>
+      <c r="AA5">
+        <v>0.115</v>
+      </c>
+      <c r="AB5">
+        <v>0.082</v>
+      </c>
+      <c r="AC5">
+        <v>0.099</v>
+      </c>
+      <c r="AD5">
+        <v>0.062</v>
+      </c>
+      <c r="AE5">
+        <v>0.061</v>
+      </c>
+      <c r="AF5">
+        <v>0.039</v>
+      </c>
+      <c r="AG5">
+        <v>0.045</v>
+      </c>
+      <c r="AH5">
+        <v>0.015</v>
+      </c>
+      <c r="AI5">
+        <v>0.018</v>
+      </c>
+      <c r="AJ5">
+        <v>0.009</v>
+      </c>
+      <c r="AK5">
+        <v>0.008</v>
+      </c>
+      <c r="AL5">
+        <v>0.004</v>
+      </c>
+      <c r="AM5">
+        <v>0.004</v>
+      </c>
+      <c r="AN5">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
+      <c r="A6">
+        <v>824768</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>4.672</v>
+      </c>
+      <c r="F6">
+        <v>5.425</v>
+      </c>
+      <c r="G6">
+        <v>0.395</v>
+      </c>
+      <c r="H6">
+        <v>0.605</v>
+      </c>
+      <c r="I6">
+        <v>0.216</v>
+      </c>
+      <c r="J6">
+        <v>0.075</v>
+      </c>
+      <c r="K6">
+        <v>0.105</v>
+      </c>
+      <c r="L6">
+        <v>0.323</v>
+      </c>
+      <c r="M6">
+        <v>0.104</v>
+      </c>
+      <c r="N6">
+        <v>0.177</v>
+      </c>
+      <c r="O6">
+        <v>0.54</v>
+      </c>
+      <c r="P6">
+        <v>2.508</v>
+      </c>
+      <c r="Q6">
+        <v>3.356</v>
+      </c>
+      <c r="R6">
+        <v>0.326</v>
+      </c>
+      <c r="S6">
+        <v>0.542</v>
+      </c>
+      <c r="T6">
+        <v>0.0</v>
+      </c>
+      <c r="U6">
+        <v>0.008</v>
+      </c>
+      <c r="V6">
+        <v>0.009</v>
+      </c>
+      <c r="W6">
+        <v>0.041</v>
+      </c>
+      <c r="X6">
+        <v>0.034</v>
+      </c>
+      <c r="Y6">
+        <v>0.068</v>
+      </c>
+      <c r="Z6">
+        <v>0.061</v>
+      </c>
+      <c r="AA6">
+        <v>0.101</v>
+      </c>
+      <c r="AB6">
+        <v>0.071</v>
+      </c>
+      <c r="AC6">
+        <v>0.102</v>
+      </c>
+      <c r="AD6">
+        <v>0.065</v>
+      </c>
+      <c r="AE6">
+        <v>0.093</v>
+      </c>
+      <c r="AF6">
+        <v>0.059</v>
+      </c>
+      <c r="AG6">
+        <v>0.08</v>
+      </c>
+      <c r="AH6">
+        <v>0.04</v>
+      </c>
+      <c r="AI6">
+        <v>0.051</v>
+      </c>
+      <c r="AJ6">
+        <v>0.028</v>
+      </c>
+      <c r="AK6">
+        <v>0.029</v>
+      </c>
+      <c r="AL6">
+        <v>0.014</v>
+      </c>
+      <c r="AM6">
+        <v>0.016</v>
+      </c>
+      <c r="AN6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40">
+      <c r="A7">
+        <v>823466</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7">
+        <v>3.492</v>
+      </c>
+      <c r="F7">
+        <v>4.807</v>
+      </c>
+      <c r="G7">
+        <v>0.324</v>
+      </c>
+      <c r="H7">
+        <v>0.676</v>
+      </c>
+      <c r="I7">
+        <v>0.155</v>
+      </c>
+      <c r="J7">
+        <v>0.071</v>
+      </c>
+      <c r="K7">
+        <v>0.098</v>
+      </c>
+      <c r="L7">
+        <v>0.352</v>
+      </c>
+      <c r="M7">
+        <v>0.126</v>
+      </c>
+      <c r="N7">
+        <v>0.198</v>
+      </c>
+      <c r="O7">
+        <v>0.464</v>
+      </c>
+      <c r="P7">
+        <v>1.835</v>
+      </c>
+      <c r="Q7">
+        <v>2.637</v>
+      </c>
+      <c r="R7">
+        <v>0.324</v>
+      </c>
+      <c r="S7">
+        <v>0.513</v>
+      </c>
+      <c r="T7">
+        <v>0.0</v>
+      </c>
+      <c r="U7">
+        <v>0.022</v>
+      </c>
+      <c r="V7">
+        <v>0.025</v>
+      </c>
+      <c r="W7">
+        <v>0.064</v>
+      </c>
+      <c r="X7">
+        <v>0.058</v>
+      </c>
+      <c r="Y7">
+        <v>0.103</v>
+      </c>
+      <c r="Z7">
+        <v>0.077</v>
+      </c>
+      <c r="AA7">
+        <v>0.115</v>
+      </c>
+      <c r="AB7">
+        <v>0.088</v>
+      </c>
+      <c r="AC7">
+        <v>0.116</v>
+      </c>
+      <c r="AD7">
+        <v>0.068</v>
+      </c>
+      <c r="AE7">
+        <v>0.075</v>
+      </c>
+      <c r="AF7">
+        <v>0.04</v>
+      </c>
+      <c r="AG7">
+        <v>0.048</v>
+      </c>
+      <c r="AH7">
+        <v>0.024</v>
+      </c>
+      <c r="AI7">
+        <v>0.027</v>
+      </c>
+      <c r="AJ7">
+        <v>0.014</v>
+      </c>
+      <c r="AK7">
+        <v>0.015</v>
+      </c>
+      <c r="AL7">
+        <v>0.007</v>
+      </c>
+      <c r="AM7">
+        <v>0.005</v>
+      </c>
+      <c r="AN7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40">
+      <c r="A8">
+        <v>823794</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <v>4.318</v>
+      </c>
+      <c r="F8">
+        <v>3.957</v>
+      </c>
+      <c r="G8">
+        <v>0.517</v>
+      </c>
+      <c r="H8">
+        <v>0.483</v>
+      </c>
+      <c r="I8">
+        <v>0.288</v>
+      </c>
+      <c r="J8">
+        <v>0.1</v>
+      </c>
+      <c r="K8">
+        <v>0.129</v>
+      </c>
+      <c r="L8">
+        <v>0.22</v>
+      </c>
+      <c r="M8">
+        <v>0.091</v>
+      </c>
+      <c r="N8">
+        <v>0.173</v>
+      </c>
+      <c r="O8">
+        <v>0.448</v>
+      </c>
+      <c r="P8">
+        <v>2.012</v>
+      </c>
+      <c r="Q8">
+        <v>2.072</v>
+      </c>
+      <c r="R8">
+        <v>0.412</v>
+      </c>
+      <c r="S8">
+        <v>0.408</v>
+      </c>
+      <c r="T8">
+        <v>0.001</v>
+      </c>
+      <c r="U8">
+        <v>0.025</v>
+      </c>
+      <c r="V8">
+        <v>0.024</v>
+      </c>
+      <c r="W8">
+        <v>0.079</v>
+      </c>
+      <c r="X8">
+        <v>0.058</v>
+      </c>
+      <c r="Y8">
+        <v>0.103</v>
+      </c>
+      <c r="Z8">
+        <v>0.081</v>
+      </c>
+      <c r="AA8">
+        <v>0.111</v>
+      </c>
+      <c r="AB8">
+        <v>0.086</v>
+      </c>
+      <c r="AC8">
+        <v>0.097</v>
+      </c>
+      <c r="AD8">
+        <v>0.059</v>
+      </c>
+      <c r="AE8">
+        <v>0.072</v>
+      </c>
+      <c r="AF8">
+        <v>0.047</v>
+      </c>
+      <c r="AG8">
+        <v>0.042</v>
+      </c>
+      <c r="AH8">
+        <v>0.031</v>
+      </c>
+      <c r="AI8">
+        <v>0.029</v>
+      </c>
+      <c r="AJ8">
+        <v>0.012</v>
+      </c>
+      <c r="AK8">
+        <v>0.011</v>
+      </c>
+      <c r="AL8">
+        <v>0.011</v>
+      </c>
+      <c r="AM8">
+        <v>0.008</v>
+      </c>
+      <c r="AN8">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40">
+      <c r="A9">
+        <v>824443</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9">
+        <v>3.725</v>
+      </c>
+      <c r="F9">
+        <v>4.268</v>
+      </c>
+      <c r="G9">
+        <v>0.414</v>
+      </c>
+      <c r="H9">
+        <v>0.586</v>
+      </c>
+      <c r="I9">
+        <v>0.205</v>
+      </c>
+      <c r="J9">
+        <v>0.094</v>
+      </c>
+      <c r="K9">
+        <v>0.115</v>
+      </c>
+      <c r="L9">
+        <v>0.273</v>
+      </c>
+      <c r="M9">
+        <v>0.114</v>
+      </c>
+      <c r="N9">
+        <v>0.199</v>
+      </c>
+      <c r="O9">
+        <v>0.417</v>
+      </c>
+      <c r="P9">
+        <v>1.793</v>
+      </c>
+      <c r="Q9">
+        <v>2.312</v>
+      </c>
+      <c r="R9">
+        <v>0.349</v>
+      </c>
+      <c r="S9">
+        <v>0.472</v>
+      </c>
+      <c r="T9">
+        <v>0.0</v>
+      </c>
+      <c r="U9">
+        <v>0.027</v>
+      </c>
+      <c r="V9">
+        <v>0.023</v>
+      </c>
+      <c r="W9">
+        <v>0.079</v>
+      </c>
+      <c r="X9">
+        <v>0.072</v>
+      </c>
+      <c r="Y9">
+        <v>0.107</v>
+      </c>
+      <c r="Z9">
+        <v>0.084</v>
+      </c>
+      <c r="AA9">
+        <v>0.121</v>
+      </c>
+      <c r="AB9">
+        <v>0.074</v>
+      </c>
+      <c r="AC9">
+        <v>0.1</v>
+      </c>
+      <c r="AD9">
+        <v>0.064</v>
+      </c>
+      <c r="AE9">
+        <v>0.069</v>
+      </c>
+      <c r="AF9">
+        <v>0.04</v>
+      </c>
+      <c r="AG9">
+        <v>0.045</v>
+      </c>
+      <c r="AH9">
+        <v>0.023</v>
+      </c>
+      <c r="AI9">
+        <v>0.024</v>
+      </c>
+      <c r="AJ9">
         <v>0.013</v>
       </c>
-      <c r="V2">
+      <c r="AK9">
+        <v>0.012</v>
+      </c>
+      <c r="AL9">
+        <v>0.006</v>
+      </c>
+      <c r="AM9">
+        <v>0.007</v>
+      </c>
+      <c r="AN9">
+        <v>0.009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40">
+      <c r="A10">
+        <v>824522</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10">
+        <v>3.969</v>
+      </c>
+      <c r="F10">
+        <v>4.93</v>
+      </c>
+      <c r="G10">
+        <v>0.37</v>
+      </c>
+      <c r="H10">
+        <v>0.63</v>
+      </c>
+      <c r="I10">
+        <v>0.182</v>
+      </c>
+      <c r="J10">
+        <v>0.084</v>
+      </c>
+      <c r="K10">
+        <v>0.104</v>
+      </c>
+      <c r="L10">
+        <v>0.321</v>
+      </c>
+      <c r="M10">
+        <v>0.128</v>
+      </c>
+      <c r="N10">
+        <v>0.181</v>
+      </c>
+      <c r="O10">
+        <v>0.462</v>
+      </c>
+      <c r="P10">
+        <v>1.742</v>
+      </c>
+      <c r="Q10">
+        <v>2.843</v>
+      </c>
+      <c r="R10">
+        <v>0.281</v>
+      </c>
+      <c r="S10">
+        <v>0.555</v>
+      </c>
+      <c r="T10">
+        <v>0.0</v>
+      </c>
+      <c r="U10">
+        <v>0.017</v>
+      </c>
+      <c r="V10">
+        <v>0.02</v>
+      </c>
+      <c r="W10">
+        <v>0.047</v>
+      </c>
+      <c r="X10">
+        <v>0.058</v>
+      </c>
+      <c r="Y10">
+        <v>0.09</v>
+      </c>
+      <c r="Z10">
+        <v>0.07</v>
+      </c>
+      <c r="AA10">
+        <v>0.124</v>
+      </c>
+      <c r="AB10">
+        <v>0.081</v>
+      </c>
+      <c r="AC10">
+        <v>0.103</v>
+      </c>
+      <c r="AD10">
+        <v>0.068</v>
+      </c>
+      <c r="AE10">
+        <v>0.071</v>
+      </c>
+      <c r="AF10">
+        <v>0.053</v>
+      </c>
+      <c r="AG10">
+        <v>0.056</v>
+      </c>
+      <c r="AH10">
+        <v>0.03</v>
+      </c>
+      <c r="AI10">
+        <v>0.035</v>
+      </c>
+      <c r="AJ10">
         <v>0.018</v>
       </c>
-      <c r="W2">
-        <v>0.048</v>
-      </c>
-      <c r="X2">
+      <c r="AK10">
+        <v>0.019</v>
+      </c>
+      <c r="AL10">
+        <v>0.011</v>
+      </c>
+      <c r="AM10">
+        <v>0.009</v>
+      </c>
+      <c r="AN10">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40">
+      <c r="A11">
+        <v>824846</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>4.619</v>
+      </c>
+      <c r="F11">
+        <v>5.132</v>
+      </c>
+      <c r="G11">
+        <v>0.435</v>
+      </c>
+      <c r="H11">
+        <v>0.565</v>
+      </c>
+      <c r="I11">
+        <v>0.246</v>
+      </c>
+      <c r="J11">
+        <v>0.079</v>
+      </c>
+      <c r="K11">
+        <v>0.111</v>
+      </c>
+      <c r="L11">
+        <v>0.288</v>
+      </c>
+      <c r="M11">
+        <v>0.101</v>
+      </c>
+      <c r="N11">
+        <v>0.175</v>
+      </c>
+      <c r="O11">
+        <v>0.533</v>
+      </c>
+      <c r="P11">
+        <v>2.596</v>
+      </c>
+      <c r="Q11">
+        <v>3.093</v>
+      </c>
+      <c r="R11">
+        <v>0.392</v>
+      </c>
+      <c r="S11">
+        <v>0.484</v>
+      </c>
+      <c r="T11">
+        <v>0.0</v>
+      </c>
+      <c r="U11">
+        <v>0.01</v>
+      </c>
+      <c r="V11">
+        <v>0.011</v>
+      </c>
+      <c r="W11">
+        <v>0.04</v>
+      </c>
+      <c r="X11">
+        <v>0.039</v>
+      </c>
+      <c r="Y11">
+        <v>0.078</v>
+      </c>
+      <c r="Z11">
+        <v>0.065</v>
+      </c>
+      <c r="AA11">
+        <v>0.099</v>
+      </c>
+      <c r="AB11">
+        <v>0.072</v>
+      </c>
+      <c r="AC11">
+        <v>0.111</v>
+      </c>
+      <c r="AD11">
+        <v>0.069</v>
+      </c>
+      <c r="AE11">
+        <v>0.09</v>
+      </c>
+      <c r="AF11">
+        <v>0.061</v>
+      </c>
+      <c r="AG11">
+        <v>0.066</v>
+      </c>
+      <c r="AH11">
         <v>0.041</v>
       </c>
-      <c r="Y2">
-        <v>0.086</v>
-      </c>
-      <c r="Z2">
-        <v>0.068</v>
-      </c>
-      <c r="AA2">
-        <v>0.106</v>
-      </c>
-      <c r="AB2">
-        <v>0.082</v>
-      </c>
-      <c r="AC2">
-        <v>0.103</v>
-      </c>
-      <c r="AD2">
-        <v>0.068</v>
-      </c>
-      <c r="AE2">
-        <v>0.095</v>
-      </c>
-      <c r="AF2">
-        <v>0.055</v>
-      </c>
-      <c r="AG2">
-        <v>0.065</v>
-      </c>
-      <c r="AH2">
-        <v>0.037</v>
-      </c>
-      <c r="AI2">
-        <v>0.037</v>
-      </c>
-      <c r="AJ2">
+      <c r="AI11">
+        <v>0.043</v>
+      </c>
+      <c r="AJ11">
+        <v>0.029</v>
+      </c>
+      <c r="AK11">
+        <v>0.026</v>
+      </c>
+      <c r="AL11">
+        <v>0.014</v>
+      </c>
+      <c r="AM11">
+        <v>0.012</v>
+      </c>
+      <c r="AN11">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40">
+      <c r="A12">
+        <v>825088</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12">
+        <v>5.082</v>
+      </c>
+      <c r="F12">
+        <v>4.387</v>
+      </c>
+      <c r="G12">
+        <v>0.54</v>
+      </c>
+      <c r="H12">
+        <v>0.46</v>
+      </c>
+      <c r="I12">
+        <v>0.314</v>
+      </c>
+      <c r="J12">
+        <v>0.107</v>
+      </c>
+      <c r="K12">
+        <v>0.118</v>
+      </c>
+      <c r="L12">
+        <v>0.196</v>
+      </c>
+      <c r="M12">
+        <v>0.09</v>
+      </c>
+      <c r="N12">
+        <v>0.174</v>
+      </c>
+      <c r="O12">
+        <v>0.473</v>
+      </c>
+      <c r="P12">
+        <v>2.8</v>
+      </c>
+      <c r="Q12">
+        <v>2.246</v>
+      </c>
+      <c r="R12">
+        <v>0.498</v>
+      </c>
+      <c r="S12">
+        <v>0.353</v>
+      </c>
+      <c r="T12">
+        <v>0.0</v>
+      </c>
+      <c r="U12">
+        <v>0.011</v>
+      </c>
+      <c r="V12">
+        <v>0.014</v>
+      </c>
+      <c r="W12">
+        <v>0.044</v>
+      </c>
+      <c r="X12">
+        <v>0.041</v>
+      </c>
+      <c r="Y12">
+        <v>0.091</v>
+      </c>
+      <c r="Z12">
+        <v>0.07</v>
+      </c>
+      <c r="AA12">
+        <v>0.107</v>
+      </c>
+      <c r="AB12">
+        <v>0.072</v>
+      </c>
+      <c r="AC12">
+        <v>0.114</v>
+      </c>
+      <c r="AD12">
+        <v>0.063</v>
+      </c>
+      <c r="AE12">
+        <v>0.084</v>
+      </c>
+      <c r="AF12">
+        <v>0.052</v>
+      </c>
+      <c r="AG12">
+        <v>0.059</v>
+      </c>
+      <c r="AH12">
+        <v>0.04</v>
+      </c>
+      <c r="AI12">
+        <v>0.04</v>
+      </c>
+      <c r="AJ12">
+        <v>0.025</v>
+      </c>
+      <c r="AK12">
         <v>0.022</v>
       </c>
-      <c r="AK2">
-        <v>0.017</v>
-      </c>
-      <c r="AL2">
-        <v>0.011</v>
-      </c>
-      <c r="AM2">
-        <v>0.009</v>
-      </c>
-      <c r="AN2">
-        <v>0.02</v>
+      <c r="AL12">
+        <v>0.012</v>
+      </c>
+      <c r="AM12">
+        <v>0.013</v>
+      </c>
+      <c r="AN12">
+        <v>0.024</v>
       </c>
     </row>
   </sheetData>
